--- a/Report of Foresty_20251127/林業署前後測結果/進階班/圖表-進階班_2025.xlsx
+++ b/Report of Foresty_20251127/林業署前後測結果/進階班/圖表-進階班_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R\test\Macaca-population-trend\Report of Foresty_2025\林業署前後測結果\進階班\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R\test\Macaca-population-trend\Report of Foresty_20251127\林業署前後測結果\進階班\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F4DB8E-6C33-493B-BD76-28EE2E282044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B59F77C-0E26-4221-BE9B-B82607D11550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12840" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28590" yWindow="-1065" windowWidth="16410" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DT" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DT!$A$1:$AY$51</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">總分!$E$2:$E$51</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">總分!$F$2:$F$51</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">總分!$F$2:$F$51</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">總分!$E$2:$E$51</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">總分!$F$2:$F$51</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">總分!$E$2:$E$51</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">總分!$F$1</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">總分!$F$2:$F$51</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">總分!$E$2:$E$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -763,10 +772,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2907,6 +2916,92 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1595950" cy="328295"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="文字方塊 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1313B24-0D48-9FAF-9988-E0D838D1E500}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10620375" y="7800975"/>
+          <a:ext cx="1595950" cy="328295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>n</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" baseline="0">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> = 25, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" i="1" baseline="0">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>p</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" baseline="0">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> &lt;0.001 </a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11664,255 +11759,255 @@
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>138</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f>D3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>96</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <f>E3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>96</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f>F3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>92</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f>G3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>96</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <f>H3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>80</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <f>I3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>84</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <f>J3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>84</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <f>K3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>52</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <f>L3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>76</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <f>M3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>68</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <f>N3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>68</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="5">
         <f>O3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>96</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="5">
         <f>P3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>88</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="5">
         <f>Q3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>76</v>
       </c>
-      <c r="R5" s="6">
+      <c r="R5" s="5">
         <f>R3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>52</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="5">
         <f>S3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>96</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="5">
         <f>T3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>92</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="5">
         <f>U3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>96</v>
       </c>
-      <c r="V5" s="6">
+      <c r="V5" s="5">
         <f>V3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>88</v>
       </c>
-      <c r="W5" s="6">
+      <c r="W5" s="5">
         <f>W3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>76</v>
       </c>
-      <c r="X5" s="6">
+      <c r="X5" s="5">
         <f>X3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>80</v>
       </c>
-      <c r="Y5" s="6">
+      <c r="Y5" s="5">
         <f>Y3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>64</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="Z5" s="5">
         <f>Z3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>60</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AA5" s="5">
         <f>AA3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>56.000000000000007</v>
       </c>
-      <c r="AB5" s="6">
+      <c r="AB5" s="5">
         <f>AB3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>56.000000000000007</v>
       </c>
-      <c r="AC5" s="6">
+      <c r="AC5" s="5">
         <f>AC3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>44</v>
       </c>
-      <c r="AD5" s="6">
+      <c r="AD5" s="5">
         <f>AD3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>44</v>
       </c>
-      <c r="AE5" s="6">
+      <c r="AE5" s="5">
         <f>AE3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>68</v>
       </c>
-      <c r="AF5" s="6">
+      <c r="AF5" s="5">
         <f>AF3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>68</v>
       </c>
-      <c r="AG5" s="6">
+      <c r="AG5" s="5">
         <f>AG3/COUNTIF(DT!$H:$H,各題_整體!$C5)*100</f>
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f>D4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <f>E4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <f>F4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <f>G4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <f>H4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>84</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <f>I4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <f>J4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <f>K4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>80</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <f>L4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <f>M4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <f>N4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <f>O4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <f>P4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>88</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <f>Q4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>76</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="5">
         <f>R4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>52</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <f>S4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="5">
         <f>T4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>100</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="5">
         <f>U4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6" s="5">
         <f>V4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>84</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="5">
         <f>W4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>92</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="5">
         <f>X4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="5">
         <f>Y4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>76</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6" s="5">
         <f>Z4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>88</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AA6" s="5">
         <f>AA4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>88</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="5">
         <f>AB4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
-      <c r="AC6" s="6">
+      <c r="AC6" s="5">
         <f>AC4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>80</v>
       </c>
-      <c r="AD6" s="6">
+      <c r="AD6" s="5">
         <f>AD4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>84</v>
       </c>
-      <c r="AE6" s="6">
+      <c r="AE6" s="5">
         <f>AE4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>68</v>
       </c>
-      <c r="AF6" s="6">
+      <c r="AF6" s="5">
         <f>AF4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>68</v>
       </c>
-      <c r="AG6" s="6">
+      <c r="AG6" s="5">
         <f>AG4/COUNTIF(DT!$H:$H,各題_整體!$C6)*100</f>
         <v>96</v>
       </c>
